--- a/doc/System_overview.xlsx
+++ b/doc/System_overview.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/zsolt_laszlo_capgemini_com/Documents/Desktop/P_Diploma/TSC/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculta\TSC\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3396A023-DB80-4185-9E40-3DC1A252B5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6FC752-00B9-4DBF-8E95-DA4CC62304B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3031D013-B3F9-406A-A259-83985C063323}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{3031D013-B3F9-406A-A259-83985C063323}"/>
   </bookViews>
   <sheets>
     <sheet name="registers" sheetId="1" r:id="rId1"/>
     <sheet name="interfaces" sheetId="2" r:id="rId2"/>
+    <sheet name="opcodes" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
     <author>Laszlo, Zsolt</author>
   </authors>
   <commentList>
-    <comment ref="K28" authorId="0" shapeId="0" xr:uid="{5164CC38-BB99-4F01-B50B-00F2E8D39806}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{5164CC38-BB99-4F01-B50B-00F2E8D39806}">
       <text>
         <r>
           <rPr>
@@ -67,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0" xr:uid="{9F4ED8B8-1157-492F-BC39-4BF0CF92F1F0}">
+    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{9F4ED8B8-1157-492F-BC39-4BF0CF92F1F0}">
       <text>
         <r>
           <rPr>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="132">
   <si>
     <t>reg</t>
   </si>
@@ -177,10 +178,6 @@
   </si>
   <si>
     <t>WC</t>
-  </si>
-  <si>
-    <t>[0] -&gt; start
-[1]-&gt;sw_reset</t>
   </si>
   <si>
     <t>[0]-&gt;op_done
@@ -212,17 +209,11 @@
     <t>number of operations to be done</t>
   </si>
   <si>
-    <t>control, auto clear, 11 illegal</t>
-  </si>
-  <si>
     <t>while the system is working the busy field of status register is asserted
 the op_cnt field counts the number of operations done by the system</t>
   </si>
   <si>
     <t>interrupt vector to be read when the intterupt request is asserted</t>
-  </si>
-  <si>
-    <t>RC</t>
   </si>
   <si>
     <t>setting what can set the interrupt
@@ -495,13 +486,32 @@
   </si>
   <si>
     <t>[3:0] -&gt; op_code</t>
+  </si>
+  <si>
+    <t>reset value</t>
+  </si>
+  <si>
+    <t>0x03</t>
+  </si>
+  <si>
+    <t>RW -&gt; read &amp; write
+WC -&gt; write only &amp; autoclear
+R -&gt; read only</t>
+  </si>
+  <si>
+    <t>control, auto clear, simultaniously asserting start and reset is illegal</t>
+  </si>
+  <si>
+    <t>[0] -&gt; start
+[1]-&gt;sw_reset
+[2]-&gt;clear_irq</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,6 +547,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -601,7 +618,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -720,14 +737,168 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -740,16 +911,14 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
+      <left/>
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -761,10 +930,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
@@ -777,35 +957,22 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -838,12 +1005,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -867,39 +1028,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -918,38 +1046,124 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1344,19 +1558,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F427FF9-E496-4410-BCC6-3FEB61F6ED55}">
-  <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F427FF9-E496-4410-BCC6-3FEB61F6ED55}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1372,8 +1587,11 @@
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F1" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -1387,10 +1605,13 @@
         <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
@@ -1404,10 +1625,13 @@
         <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -1421,10 +1645,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
@@ -1438,27 +1665,33 @@
         <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
@@ -1466,16 +1699,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
@@ -1483,16 +1719,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>15</v>
       </c>
@@ -1500,712 +1739,740 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E13" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E14" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0</v>
-      </c>
-      <c r="I14" s="16">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L14" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E15" s="29"/>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9">
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <v>1</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L15" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E16" s="29"/>
-      <c r="F16" s="17">
-        <v>0</v>
-      </c>
-      <c r="G16" s="17">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>1</v>
-      </c>
-      <c r="I16" s="18">
-        <v>0</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E17" s="29"/>
-      <c r="F17" s="17">
-        <v>0</v>
-      </c>
-      <c r="G17" s="17">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>1</v>
-      </c>
-      <c r="I17" s="18">
-        <v>1</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L17" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E18" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="19">
-        <v>0</v>
-      </c>
-      <c r="G18" s="19">
-        <v>1</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E19" s="30"/>
-      <c r="F19" s="19">
-        <v>0</v>
-      </c>
-      <c r="G19" s="19">
-        <v>1</v>
-      </c>
-      <c r="H19" s="9">
-        <v>0</v>
-      </c>
-      <c r="I19" s="18">
-        <v>1</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L19" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E20" s="30"/>
-      <c r="F20" s="19">
-        <v>0</v>
-      </c>
-      <c r="G20" s="19">
-        <v>1</v>
-      </c>
-      <c r="H20" s="9">
-        <v>1</v>
-      </c>
-      <c r="I20" s="18">
-        <v>0</v>
-      </c>
-      <c r="J20" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E21" s="30"/>
-      <c r="F21" s="19">
-        <v>0</v>
-      </c>
-      <c r="G21" s="19">
-        <v>1</v>
-      </c>
-      <c r="H21" s="9">
-        <v>1</v>
-      </c>
-      <c r="I21" s="18">
-        <v>1</v>
-      </c>
-      <c r="J21" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="L21" s="25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E22" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="20">
-        <v>1</v>
-      </c>
-      <c r="G22" s="20">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>0</v>
-      </c>
-      <c r="I22" s="18">
-        <v>0</v>
-      </c>
-      <c r="J22" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="L22" s="25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E23" s="31"/>
-      <c r="F23" s="20">
-        <v>1</v>
-      </c>
-      <c r="G23" s="20">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>0</v>
-      </c>
-      <c r="I23" s="18">
-        <v>1</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="L23" s="25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E24" s="31"/>
-      <c r="F24" s="20">
-        <v>1</v>
-      </c>
-      <c r="G24" s="20">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>1</v>
-      </c>
-      <c r="I24" s="18">
-        <v>0</v>
-      </c>
-      <c r="J24" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="L24" s="25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E25" s="31"/>
-      <c r="F25" s="20">
-        <v>1</v>
-      </c>
-      <c r="G25" s="20">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>1</v>
-      </c>
-      <c r="I25" s="18">
-        <v>1</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="L25" s="25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E26" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="21">
-        <v>1</v>
-      </c>
-      <c r="G26" s="21">
-        <v>1</v>
-      </c>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="L26" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E27" s="32"/>
-      <c r="F27" s="21">
-        <v>1</v>
-      </c>
-      <c r="G27" s="21">
-        <v>1</v>
-      </c>
-      <c r="H27" s="9">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <v>1</v>
-      </c>
-      <c r="J27" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="L27" s="25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E28" s="32"/>
-      <c r="F28" s="21">
-        <v>1</v>
-      </c>
-      <c r="G28" s="21">
-        <v>1</v>
-      </c>
-      <c r="H28" s="9">
-        <v>1</v>
-      </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E29" s="32"/>
-      <c r="F29" s="21">
-        <v>1</v>
-      </c>
-      <c r="G29" s="21">
-        <v>1</v>
-      </c>
-      <c r="H29" s="9">
-        <v>1</v>
-      </c>
-      <c r="I29" s="18">
-        <v>1</v>
-      </c>
-      <c r="J29" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L29" s="25" t="s">
-        <v>67</v>
+        <v>37</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="E12" s="75" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="E26:E29"/>
-  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B74E85BE-8A35-4CDE-B704-E50485B42095}">
-  <dimension ref="B2:F16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="E1" s="34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="C2" s="24">
+        <v>1</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="44"/>
+      <c r="B3" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="C3" s="21">
+        <v>1</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="44"/>
+      <c r="B4" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="C4" s="21">
+        <v>1</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="44"/>
+      <c r="B5" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="21">
+        <v>6</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
+      <c r="B6" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="21">
+        <v>32</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="44"/>
+      <c r="B7" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="21">
+        <v>32</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="44"/>
+      <c r="B8" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="21">
+        <v>1</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="45"/>
+      <c r="B9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="28">
+        <v>1</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="26">
+        <v>1</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="47"/>
+      <c r="B11" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="17">
+        <v>1</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="47"/>
+      <c r="B12" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="37">
-        <v>1</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="49"/>
-      <c r="C4" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="34">
-        <v>1</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="49"/>
-      <c r="C5" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="34">
-        <v>1</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="49"/>
-      <c r="C6" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="34">
-        <v>6</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="49"/>
-      <c r="C7" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="34">
-        <v>32</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="49"/>
-      <c r="C8" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="34">
-        <v>32</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="49"/>
-      <c r="C9" s="33" t="s">
+      <c r="C12" s="17">
+        <v>16</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="47"/>
+      <c r="B13" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="17">
+        <v>8</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="48"/>
+      <c r="B14" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="30">
+        <v>8</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="34">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="50"/>
-      <c r="C10" s="40" t="s">
+      <c r="E14" s="40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="33">
+        <v>1</v>
+      </c>
+      <c r="D15" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="41">
-        <v>1</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="39">
-        <v>1</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
-      <c r="C12" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="19">
-        <v>1</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
-      <c r="C13" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="19">
-        <v>16</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F13" s="35" t="s">
+      <c r="E15" s="41" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="52"/>
-      <c r="C14" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="19">
-        <v>8</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="53"/>
-      <c r="C15" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="45">
-        <v>8</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="44" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="42">
-        <v>1</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B3:B10"/>
-    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B502E5-BDC3-46AE-B0FD-DE6CC1EF7D03}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="50">
+        <v>0</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="72" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="55"/>
+      <c r="B3" s="51">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+      <c r="E3" s="16">
+        <v>1</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="55"/>
+      <c r="B4" s="51">
+        <v>0</v>
+      </c>
+      <c r="C4" s="15">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9">
+        <v>1</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="56"/>
+      <c r="B5" s="51">
+        <v>0</v>
+      </c>
+      <c r="C5" s="15">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16">
+        <v>1</v>
+      </c>
+      <c r="F5" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="52">
+        <v>0</v>
+      </c>
+      <c r="C6" s="17">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16">
+        <v>0</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="58"/>
+      <c r="B7" s="52">
+        <v>0</v>
+      </c>
+      <c r="C7" s="17">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16">
+        <v>1</v>
+      </c>
+      <c r="F7" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="73" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="58"/>
+      <c r="B8" s="52">
+        <v>0</v>
+      </c>
+      <c r="C8" s="17">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0</v>
+      </c>
+      <c r="F8" s="70" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="59"/>
+      <c r="B9" s="52">
+        <v>0</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="16">
+        <v>1</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="53">
+        <v>1</v>
+      </c>
+      <c r="C10" s="18">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+      <c r="F10" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="61"/>
+      <c r="B11" s="53">
+        <v>1</v>
+      </c>
+      <c r="C11" s="18">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <v>1</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="61"/>
+      <c r="B12" s="53">
+        <v>1</v>
+      </c>
+      <c r="C12" s="18">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="62"/>
+      <c r="B13" s="53">
+        <v>1</v>
+      </c>
+      <c r="C13" s="18">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="16">
+        <v>1</v>
+      </c>
+      <c r="F13" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="54">
+        <v>1</v>
+      </c>
+      <c r="C14" s="19">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0</v>
+      </c>
+      <c r="F14" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="64"/>
+      <c r="B15" s="54">
+        <v>1</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16">
+        <v>1</v>
+      </c>
+      <c r="F15" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="64"/>
+      <c r="B16" s="54">
+        <v>1</v>
+      </c>
+      <c r="C16" s="19">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="73" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="65"/>
+      <c r="B17" s="54">
+        <v>1</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="16">
+        <v>1</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/doc/System_overview.xlsx
+++ b/doc/System_overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculta\TSC\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6FC752-00B9-4DBF-8E95-DA4CC62304B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEB0799-D041-4FD3-85E1-885D183D8073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{3031D013-B3F9-406A-A259-83985C063323}"/>
+    <workbookView xWindow="3870" yWindow="3150" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3031D013-B3F9-406A-A259-83985C063323}"/>
   </bookViews>
   <sheets>
     <sheet name="registers" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="134">
   <si>
     <t>reg</t>
   </si>
@@ -505,6 +505,12 @@
     <t>[0] -&gt; start
 [1]-&gt;sw_reset
 [2]-&gt;clear_irq</t>
+  </si>
+  <si>
+    <t>ira</t>
+  </si>
+  <si>
+    <t>interrup acknowlaged</t>
   </si>
 </sst>
 </file>
@@ -618,7 +624,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -737,10 +743,38 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -753,6 +787,45 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -766,22 +839,92 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
@@ -794,12 +937,27 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -810,160 +968,34 @@
         <color indexed="64"/>
       </left>
       <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -972,7 +1004,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1038,10 +1070,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1051,120 +1079,132 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1751,7 +1791,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>30</v>
       </c>
@@ -1772,7 +1812,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="53" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1786,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B74E85BE-8A35-4CDE-B704-E50485B42095}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -1796,24 +1836,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="32" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="54" t="s">
         <v>102</v>
       </c>
       <c r="B2" s="23" t="s">
@@ -1825,12 +1865,12 @@
       <c r="D2" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="33" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="44"/>
+      <c r="A3" s="55"/>
       <c r="B3" s="20" t="s">
         <v>93</v>
       </c>
@@ -1840,12 +1880,12 @@
       <c r="D3" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="34" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="A4" s="55"/>
       <c r="B4" s="20" t="s">
         <v>94</v>
       </c>
@@ -1855,12 +1895,12 @@
       <c r="D4" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="34" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+      <c r="A5" s="55"/>
       <c r="B5" s="20" t="s">
         <v>99</v>
       </c>
@@ -1870,12 +1910,12 @@
       <c r="D5" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="34" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+      <c r="A6" s="55"/>
       <c r="B6" s="20" t="s">
         <v>95</v>
       </c>
@@ -1885,12 +1925,12 @@
       <c r="D6" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="34" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="20" t="s">
         <v>96</v>
       </c>
@@ -1900,12 +1940,12 @@
       <c r="D7" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="34" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+      <c r="A8" s="55"/>
       <c r="B8" s="20" t="s">
         <v>97</v>
       </c>
@@ -1915,44 +1955,44 @@
       <c r="D8" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="34" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
-      <c r="B9" s="27" t="s">
+      <c r="A9" s="56"/>
+      <c r="B9" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="28">
-        <v>1</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="C9" s="26">
+        <v>1</v>
+      </c>
+      <c r="D9" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="35" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="26">
-        <v>1</v>
-      </c>
-      <c r="D10" s="26" t="s">
+      <c r="C10" s="71">
+        <v>1</v>
+      </c>
+      <c r="D10" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="72" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="47"/>
+      <c r="A11" s="58"/>
       <c r="B11" s="22" t="s">
         <v>104</v>
       </c>
@@ -1962,12 +2002,12 @@
       <c r="D11" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="36" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="47"/>
+      <c r="A12" s="58"/>
       <c r="B12" s="22" t="s">
         <v>105</v>
       </c>
@@ -1977,12 +2017,12 @@
       <c r="D12" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="36" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
+      <c r="A13" s="58"/>
       <c r="B13" s="22" t="s">
         <v>106</v>
       </c>
@@ -1992,46 +2032,62 @@
       <c r="D13" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="36" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="73"/>
+      <c r="B14" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="28">
         <v>8</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="37" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="49" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="33">
-        <v>1</v>
-      </c>
-      <c r="D15" s="33" t="s">
+      <c r="C15" s="76">
+        <v>1</v>
+      </c>
+      <c r="D15" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="78" t="s">
         <v>124</v>
       </c>
     </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="77"/>
+      <c r="B16" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="31">
+        <v>1</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="79" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A15:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2047,36 +2103,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="71" t="s">
+      <c r="G1" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="46" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="50">
+      <c r="B2" s="39">
         <v>0</v>
       </c>
       <c r="C2" s="12">
@@ -2088,10 +2144,10 @@
       <c r="E2" s="14">
         <v>0</v>
       </c>
-      <c r="F2" s="69" t="s">
+      <c r="F2" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="50" t="s">
         <v>39</v>
       </c>
       <c r="H2" s="11">
@@ -2099,8 +2155,8 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="55"/>
-      <c r="B3" s="51">
+      <c r="A3" s="59"/>
+      <c r="B3" s="40">
         <v>0</v>
       </c>
       <c r="C3" s="15">
@@ -2112,10 +2168,10 @@
       <c r="E3" s="16">
         <v>1</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="51" t="s">
         <v>40</v>
       </c>
       <c r="H3" s="10">
@@ -2123,8 +2179,8 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="51">
+      <c r="A4" s="59"/>
+      <c r="B4" s="40">
         <v>0</v>
       </c>
       <c r="C4" s="15">
@@ -2136,10 +2192,10 @@
       <c r="E4" s="16">
         <v>0</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="51" t="s">
         <v>41</v>
       </c>
       <c r="H4" s="10">
@@ -2147,8 +2203,8 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="56"/>
-      <c r="B5" s="51">
+      <c r="A5" s="60"/>
+      <c r="B5" s="40">
         <v>0</v>
       </c>
       <c r="C5" s="15">
@@ -2160,10 +2216,10 @@
       <c r="E5" s="16">
         <v>1</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="51" t="s">
         <v>42</v>
       </c>
       <c r="H5" s="10">
@@ -2171,10 +2227,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="52">
+      <c r="B6" s="41">
         <v>0</v>
       </c>
       <c r="C6" s="17">
@@ -2186,10 +2242,10 @@
       <c r="E6" s="16">
         <v>0</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="73" t="s">
+      <c r="G6" s="51" t="s">
         <v>52</v>
       </c>
       <c r="H6" s="10">
@@ -2197,8 +2253,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
-      <c r="B7" s="52">
+      <c r="A7" s="62"/>
+      <c r="B7" s="41">
         <v>0</v>
       </c>
       <c r="C7" s="17">
@@ -2210,10 +2266,10 @@
       <c r="E7" s="16">
         <v>1</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="51" t="s">
         <v>45</v>
       </c>
       <c r="H7" s="10">
@@ -2221,8 +2277,8 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
-      <c r="B8" s="52">
+      <c r="A8" s="62"/>
+      <c r="B8" s="41">
         <v>0</v>
       </c>
       <c r="C8" s="17">
@@ -2234,10 +2290,10 @@
       <c r="E8" s="16">
         <v>0</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="51" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="10">
@@ -2245,8 +2301,8 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
-      <c r="B9" s="52">
+      <c r="A9" s="63"/>
+      <c r="B9" s="41">
         <v>0</v>
       </c>
       <c r="C9" s="17">
@@ -2258,10 +2314,10 @@
       <c r="E9" s="16">
         <v>1</v>
       </c>
-      <c r="F9" s="70" t="s">
+      <c r="F9" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="G9" s="73" t="s">
+      <c r="G9" s="51" t="s">
         <v>51</v>
       </c>
       <c r="H9" s="10">
@@ -2269,10 +2325,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="53">
+      <c r="B10" s="42">
         <v>1</v>
       </c>
       <c r="C10" s="18">
@@ -2284,10 +2340,10 @@
       <c r="E10" s="16">
         <v>0</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="51" t="s">
         <v>80</v>
       </c>
       <c r="H10" s="10">
@@ -2295,8 +2351,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="53">
+      <c r="A11" s="65"/>
+      <c r="B11" s="42">
         <v>1</v>
       </c>
       <c r="C11" s="18">
@@ -2308,10 +2364,10 @@
       <c r="E11" s="16">
         <v>1</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="51" t="s">
         <v>46</v>
       </c>
       <c r="H11" s="10">
@@ -2319,8 +2375,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="53">
+      <c r="A12" s="65"/>
+      <c r="B12" s="42">
         <v>1</v>
       </c>
       <c r="C12" s="18">
@@ -2332,10 +2388,10 @@
       <c r="E12" s="16">
         <v>0</v>
       </c>
-      <c r="F12" s="70" t="s">
+      <c r="F12" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="51" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="10" t="s">
@@ -2343,8 +2399,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="62"/>
-      <c r="B13" s="53">
+      <c r="A13" s="66"/>
+      <c r="B13" s="42">
         <v>1</v>
       </c>
       <c r="C13" s="18">
@@ -2356,10 +2412,10 @@
       <c r="E13" s="16">
         <v>1</v>
       </c>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="73" t="s">
+      <c r="G13" s="51" t="s">
         <v>53</v>
       </c>
       <c r="H13" s="10" t="s">
@@ -2367,10 +2423,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="43">
         <v>1</v>
       </c>
       <c r="C14" s="19">
@@ -2382,10 +2438,10 @@
       <c r="E14" s="16">
         <v>0</v>
       </c>
-      <c r="F14" s="70" t="s">
+      <c r="F14" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="51" t="s">
         <v>84</v>
       </c>
       <c r="H14" s="10" t="s">
@@ -2393,8 +2449,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="64"/>
-      <c r="B15" s="54">
+      <c r="A15" s="68"/>
+      <c r="B15" s="43">
         <v>1</v>
       </c>
       <c r="C15" s="19">
@@ -2406,10 +2462,10 @@
       <c r="E15" s="16">
         <v>1</v>
       </c>
-      <c r="F15" s="70" t="s">
+      <c r="F15" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="73" t="s">
+      <c r="G15" s="51" t="s">
         <v>85</v>
       </c>
       <c r="H15" s="10" t="s">
@@ -2417,8 +2473,8 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="64"/>
-      <c r="B16" s="54">
+      <c r="A16" s="68"/>
+      <c r="B16" s="43">
         <v>1</v>
       </c>
       <c r="C16" s="19">
@@ -2430,10 +2486,10 @@
       <c r="E16" s="16">
         <v>0</v>
       </c>
-      <c r="F16" s="70" t="s">
+      <c r="F16" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="51" t="s">
         <v>86</v>
       </c>
       <c r="H16" s="10" t="s">
@@ -2441,8 +2497,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
-      <c r="B17" s="54">
+      <c r="A17" s="69"/>
+      <c r="B17" s="43">
         <v>1</v>
       </c>
       <c r="C17" s="19">
@@ -2454,10 +2510,10 @@
       <c r="E17" s="16">
         <v>1</v>
       </c>
-      <c r="F17" s="70" t="s">
+      <c r="F17" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="73" t="s">
+      <c r="G17" s="51" t="s">
         <v>87</v>
       </c>
       <c r="H17" s="10" t="s">

--- a/doc/System_overview.xlsx
+++ b/doc/System_overview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/zsolt_laszlo_capgemini_com/Documents/Desktop/P_Diploma/TSC/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3396A023-DB80-4185-9E40-3DC1A252B5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{3396A023-DB80-4185-9E40-3DC1A252B5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48B5524A-54BE-4BF7-AFF6-A80B9679CF02}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3031D013-B3F9-406A-A259-83985C063323}"/>
   </bookViews>
@@ -889,18 +889,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -930,6 +918,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -947,9 +950,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1026,6 +1026,10 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1553,7 +1557,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="45" t="s">
         <v>68</v>
       </c>
       <c r="F14" s="14">
@@ -1579,7 +1583,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E15" s="29"/>
+      <c r="E15" s="45"/>
       <c r="F15" s="17">
         <v>0</v>
       </c>
@@ -1603,7 +1607,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E16" s="29"/>
+      <c r="E16" s="45"/>
       <c r="F16" s="17">
         <v>0</v>
       </c>
@@ -1627,7 +1631,7 @@
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E17" s="29"/>
+      <c r="E17" s="45"/>
       <c r="F17" s="17">
         <v>0</v>
       </c>
@@ -1651,7 +1655,7 @@
       </c>
     </row>
     <row r="18" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="46" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="19">
@@ -1677,7 +1681,7 @@
       </c>
     </row>
     <row r="19" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E19" s="30"/>
+      <c r="E19" s="46"/>
       <c r="F19" s="19">
         <v>0</v>
       </c>
@@ -1701,7 +1705,7 @@
       </c>
     </row>
     <row r="20" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E20" s="30"/>
+      <c r="E20" s="46"/>
       <c r="F20" s="19">
         <v>0</v>
       </c>
@@ -1725,7 +1729,7 @@
       </c>
     </row>
     <row r="21" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E21" s="30"/>
+      <c r="E21" s="46"/>
       <c r="F21" s="19">
         <v>0</v>
       </c>
@@ -1749,7 +1753,7 @@
       </c>
     </row>
     <row r="22" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="47" t="s">
         <v>70</v>
       </c>
       <c r="F22" s="20">
@@ -1775,7 +1779,7 @@
       </c>
     </row>
     <row r="23" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E23" s="31"/>
+      <c r="E23" s="47"/>
       <c r="F23" s="20">
         <v>1</v>
       </c>
@@ -1799,7 +1803,7 @@
       </c>
     </row>
     <row r="24" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E24" s="31"/>
+      <c r="E24" s="47"/>
       <c r="F24" s="20">
         <v>1</v>
       </c>
@@ -1823,7 +1827,7 @@
       </c>
     </row>
     <row r="25" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E25" s="31"/>
+      <c r="E25" s="47"/>
       <c r="F25" s="20">
         <v>1</v>
       </c>
@@ -1847,7 +1851,7 @@
       </c>
     </row>
     <row r="26" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="48" t="s">
         <v>71</v>
       </c>
       <c r="F26" s="21">
@@ -1873,7 +1877,7 @@
       </c>
     </row>
     <row r="27" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E27" s="32"/>
+      <c r="E27" s="48"/>
       <c r="F27" s="21">
         <v>1</v>
       </c>
@@ -1897,7 +1901,7 @@
       </c>
     </row>
     <row r="28" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E28" s="32"/>
+      <c r="E28" s="48"/>
       <c r="F28" s="21">
         <v>1</v>
       </c>
@@ -1921,7 +1925,7 @@
       </c>
     </row>
     <row r="29" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E29" s="32"/>
+      <c r="E29" s="48"/>
       <c r="F29" s="21">
         <v>1</v>
       </c>
@@ -1968,164 +1972,164 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="43" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="37">
-        <v>1</v>
-      </c>
-      <c r="E3" s="37" t="s">
+      <c r="D3" s="33">
+        <v>1</v>
+      </c>
+      <c r="E3" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="32" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="49"/>
-      <c r="C4" s="33" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="34">
-        <v>1</v>
-      </c>
-      <c r="E4" s="34" t="s">
+      <c r="D4" s="30">
+        <v>1</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="29" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="49"/>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="34">
-        <v>1</v>
-      </c>
-      <c r="E5" s="34" t="s">
+      <c r="D5" s="30">
+        <v>1</v>
+      </c>
+      <c r="E5" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="29" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="49"/>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="30">
         <v>6</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="29" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="49"/>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="30">
         <v>32</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="29" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="49"/>
-      <c r="C8" s="33" t="s">
+      <c r="B8" s="50"/>
+      <c r="C8" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="30">
         <v>32</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="29" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="49"/>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="50"/>
+      <c r="C9" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="34">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34" t="s">
+      <c r="D9" s="30">
+        <v>1</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="29" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="50"/>
-      <c r="C10" s="40" t="s">
+      <c r="B10" s="51"/>
+      <c r="C10" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="41">
-        <v>1</v>
-      </c>
-      <c r="E10" s="41" t="s">
+      <c r="D10" s="37">
+        <v>1</v>
+      </c>
+      <c r="E10" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="36" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="39">
-        <v>1</v>
-      </c>
-      <c r="E11" s="39" t="s">
+      <c r="D11" s="35">
+        <v>1</v>
+      </c>
+      <c r="E11" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="34" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
-      <c r="C12" s="35" t="s">
+      <c r="B12" s="53"/>
+      <c r="C12" s="31" t="s">
         <v>107</v>
       </c>
       <c r="D12" s="19">
@@ -2134,13 +2138,13 @@
       <c r="E12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="31" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
-      <c r="C13" s="35" t="s">
+      <c r="B13" s="53"/>
+      <c r="C13" s="31" t="s">
         <v>108</v>
       </c>
       <c r="D13" s="19">
@@ -2149,13 +2153,13 @@
       <c r="E13" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="31" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="52"/>
-      <c r="C14" s="35" t="s">
+      <c r="B14" s="53"/>
+      <c r="C14" s="31" t="s">
         <v>109</v>
       </c>
       <c r="D14" s="19">
@@ -2164,39 +2168,39 @@
       <c r="E14" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="53"/>
-      <c r="C15" s="44" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="41">
         <v>8</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="40" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="42">
-        <v>1</v>
-      </c>
-      <c r="E16" s="42" t="s">
+      <c r="D16" s="38">
+        <v>1</v>
+      </c>
+      <c r="E16" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="42" t="s">
         <v>127</v>
       </c>
     </row>
